--- a/artfynd/A 56115-2023 artfynd.xlsx
+++ b/artfynd/A 56115-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,52 +680,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119140812</v>
+        <v>137313150</v>
       </c>
       <c r="B2" t="n">
-        <v>99096</v>
+        <v>56923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219798</v>
+        <v>100053</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Erinaceus europaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Östergarn Falhammars 1:7, Gtl</t>
+          <t>Kaupungs, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>732908</v>
+        <v>732820</v>
       </c>
       <c r="R2" t="n">
-        <v>6369399</v>
+        <v>6369415</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,27 +753,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>I äldre tallskog.</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,23 +767,144 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sebastian Bolander</t>
+          <t>Niclas Ahlberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sebastian Bolander</t>
+          <t>Niclas Ahlberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137313150</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>119140812</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Östergarn Falhammars 1:7, Gtl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>732908</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6369399</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Östergarn</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>I äldre tallskog.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/119140812</t>
         </is>
@@ -803,6 +913,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56115-2023 artfynd.xlsx
+++ b/artfynd/A 56115-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137313150</v>
       </c>
       <c r="B2" t="n">
-        <v>56923</v>
+        <v>56924</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 56115-2023 artfynd.xlsx
+++ b/artfynd/A 56115-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137313150</v>
       </c>
       <c r="B2" t="n">
-        <v>56924</v>
+        <v>56927</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
